--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512470_ELIMINGRC14FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512470_ELIMINGRC14FINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2765</v>
+        <v>8.094200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>12.2211</v>
+        <v>12.3798</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.9447</v>
+        <v>-4.2856</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8344</v>
+        <v>0.7567</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2435</v>
+        <v>-0.3131</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0779</v>
+        <v>1.0698</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1646</v>
+        <v>5.3381</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1212</v>
+        <v>2.2092</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0434</v>
+        <v>3.1289</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.3302</v>
+        <v>-4.5814</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.3647</v>
+        <v>-2.5223</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.9654</v>
+        <v>-2.0591</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5744</v>
+        <v>0.4398</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7382</v>
+        <v>0.5722</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1638</v>
+        <v>-0.1325</v>
       </c>
       <c r="V2" t="n">
-        <v>4.8671</v>
+        <v>4.9504</v>
       </c>
       <c r="W2" t="n">
-        <v>6.5184</v>
+        <v>6.6642</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.6513</v>
+        <v>-1.7138</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1717</v>
+        <v>1.4623</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0717</v>
+        <v>1.6996</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1</v>
+        <v>-0.2373</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6757</v>
+        <v>-0.6629</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2148</v>
+        <v>0.271</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8905</v>
+        <v>-0.9339</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0252</v>
+        <v>1.1449</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8652</v>
+        <v>0.9828</v>
       </c>
       <c r="L3" t="n">
-        <v>0.16</v>
+        <v>0.1621</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7009</v>
+        <v>-1.8078</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6503</v>
+        <v>-0.7118</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0505</v>
+        <v>-1.096</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2393</v>
+        <v>0.5332</v>
       </c>
       <c r="T3" t="n">
-        <v>0.847</v>
+        <v>0.3073</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3922</v>
+        <v>0.2259</v>
       </c>
       <c r="V3" t="n">
-        <v>1.008</v>
+        <v>1.0078</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1918</v>
+        <v>-0.2133</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. ISERN MAZA</t>
+          <t>D. FONT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4988</v>
+        <v>0.9594</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1237</v>
+        <v>4.2081</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6249</v>
+        <v>-3.2487</v>
       </c>
       <c r="G4" t="n">
-        <v>0.531</v>
+        <v>-0.9855</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5173</v>
+        <v>-0.47</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0137</v>
+        <v>-0.5155</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1815</v>
+        <v>1.7472</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1815</v>
+        <v>1.147</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.6002</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6505</v>
+        <v>-2.7327</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6642</v>
+        <v>-1.617</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0137</v>
+        <v>-1.1157</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2001</v>
+        <v>0.9737</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2001</v>
+        <v>1.9474</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2323</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0578</v>
+        <v>0.1025</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1745</v>
+        <v>-0.0212</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.3321</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. FONT RODRIGUEZ</t>
+          <t>X. ISERN MAZA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2081</v>
+        <v>0.8507</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2563</v>
+        <v>1.3912</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.0482</v>
+        <v>-0.5405</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9867</v>
+        <v>0.5432</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4824</v>
+        <v>0.5563</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5043</v>
+        <v>-0.0131</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5508</v>
+        <v>1.2444</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0251</v>
+        <v>1.2444</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5256</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5375</v>
+        <v>-0.7013</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5075</v>
+        <v>-0.6882</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0299</v>
+        <v>-0.0131</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0003</v>
+        <v>0.1947</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0006</v>
+        <v>0.1947</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6651</v>
+        <v>0.1128</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5534</v>
+        <v>0.1467</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1117</v>
+        <v>-0.0339</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8597</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.2592</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1949</v>
+        <v>0.2198</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1549</v>
+        <v>0.1793</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1756</v>
+        <v>0.1734</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1756</v>
+        <v>0.1734</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0193</v>
+        <v>0.0464</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0193</v>
+        <v>0.0464</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0061</v>
+        <v>-0.8243</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0148</v>
+        <v>0.4766</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0209</v>
+        <v>-1.3009</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7393</v>
+        <v>-0.7955</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6449</v>
+        <v>0.6116</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3842</v>
+        <v>-1.4071</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3614</v>
+        <v>1.4281</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9594</v>
+        <v>2.0116</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.598</v>
+        <v>-0.5835</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1007</v>
+        <v>-2.2236</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3145</v>
+        <v>-1.4</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7862</v>
+        <v>-0.8236</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2653</v>
+        <v>0.4891</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8537</v>
+        <v>0.2169</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4116</v>
+        <v>0.2722</v>
       </c>
       <c r="V7" t="n">
-        <v>0.068</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.068</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.871</v>
+        <v>-1.2192</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4078</v>
+        <v>-1.5287</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.3095</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2718</v>
+        <v>0.2203</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4199</v>
+        <v>-0.4311</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6917</v>
+        <v>0.6514</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7016</v>
+        <v>0.7518</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7016</v>
+        <v>0.7518</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4298</v>
+        <v>-0.5315</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1215</v>
+        <v>-1.1829</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6917</v>
+        <v>0.6514</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.4007</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2579</v>
+        <v>0.8973</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8914</v>
+        <v>0.6405</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3664</v>
+        <v>0.2568</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2396</v>
+        <v>-1.3263</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4285</v>
+        <v>-0.3631</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8111</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5622</v>
+        <v>-0.57</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9728</v>
+        <v>-1.0176</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4106</v>
+        <v>0.4476</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8673</v>
+        <v>0.9825</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3417</v>
+        <v>0.3823</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5256</v>
+        <v>0.6002</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4295</v>
+        <v>-1.5525</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3145</v>
+        <v>-1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.115</v>
+        <v>-0.1526</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1743</v>
+        <v>0.126</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0955</v>
+        <v>-0.1772</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2698</v>
+        <v>0.3032</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4516</v>
+        <v>-0.4927</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4516</v>
+        <v>-0.4927</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.243</v>
+        <v>-1.7915</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5283</v>
+        <v>-2.0651</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2853</v>
+        <v>0.2737</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1518</v>
+        <v>1.1056</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2217</v>
+        <v>-0.2592</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3735</v>
+        <v>1.3648</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0596</v>
+        <v>2.0963</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6998</v>
+        <v>0.7184</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3598</v>
+        <v>1.3779</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.9907</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9215</v>
+        <v>-0.9776</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0137</v>
+        <v>-0.0131</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.2012</v>
+        <v>-4.0895</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1939</v>
+        <v>0.2187</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3867</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1929</v>
+        <v>0.2907</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5682</v>
+        <v>-3.3138</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3567</v>
+        <v>-0.9875</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2115</v>
+        <v>-2.3263</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8264</v>
+        <v>-2.8566</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5955</v>
+        <v>-0.605</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2309</v>
+        <v>-2.2516</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6544</v>
+        <v>-0.5777</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0164</v>
+        <v>0.0463</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.638</v>
+        <v>-0.624</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.172</v>
+        <v>-2.2789</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.6513</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.5929</v>
+        <v>-1.6276</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0905</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7023</v>
+        <v>-0.4098</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3882</v>
+        <v>-0.3336</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.4516</v>
+        <v>-0.4927</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.4516</v>
+        <v>-0.4927</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. VICENS MOREY</t>
+          <t>N. BAQUES GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4149</v>
+        <v>-5.2916</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6458</v>
+        <v>-5.2892</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7691</v>
+        <v>-0.0024</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1156</v>
+        <v>-2.3295</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2709</v>
+        <v>-0.1298</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8447</v>
+        <v>-2.1997</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.994</v>
+        <v>-0.4613</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.678</v>
+        <v>1.4267</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.316</v>
+        <v>-1.888</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1216</v>
+        <v>-1.8682</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5929</v>
+        <v>-1.5565</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.3117</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.2006</v>
+        <v>-4.6737</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2006</v>
+        <v>-6.8158</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.1421</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1611</v>
+        <v>0.8216</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4512</v>
+        <v>0.4873</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6123</v>
+        <v>0.3343</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2598</v>
+        <v>0.89</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2598</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. BAQUES GARCIA</t>
+          <t>A. VICENS MOREY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.1845</v>
+        <v>-5.4318</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.5877</v>
+        <v>-4.4283</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4032</v>
+        <v>-1.0035</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.3447</v>
+        <v>-3.1253</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1694</v>
+        <v>-1.2921</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1753</v>
+        <v>-1.8332</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6852</v>
+        <v>-1.953</v>
       </c>
       <c r="K13" t="n">
-        <v>1.2669</v>
+        <v>-0.6645</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.9521</v>
+        <v>-1.2885</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6595</v>
+        <v>-1.1723</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4363</v>
+        <v>-0.6276</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2232</v>
+        <v>-0.5447</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.8014</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q13" t="n">
-        <v>-7.002</v>
+        <v>-2.1421</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2006</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1019</v>
+        <v>0.1151</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.36</v>
+        <v>-0.3332</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4619</v>
+        <v>0.4483</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8597</v>
+        <v>-0.2795</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4596</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5999</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.177299999999999</v>
+        <v>-7.6121</v>
       </c>
       <c r="E14" t="n">
-        <v>2.772799999999998</v>
+        <v>5.533899999999996</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.9502</v>
+        <v>-13.1459</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.286</v>
+        <v>-8.5261</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.9991</v>
+        <v>-3.079</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.2869</v>
+        <v>-5.4471</v>
       </c>
       <c r="J14" t="n">
-        <v>10.6184</v>
+        <v>11.7818</v>
       </c>
       <c r="K14" t="n">
-        <v>9.467999999999996</v>
+        <v>10.256</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1503</v>
+        <v>1.5258</v>
       </c>
       <c r="M14" t="n">
-        <v>-18.9044</v>
+        <v>-20.308</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.467</v>
+        <v>-13.3352</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.4371</v>
+        <v>-6.9729</v>
       </c>
       <c r="P14" t="n">
-        <v>-9.002500000000001</v>
+        <v>-8.763200000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-21.006</v>
+        <v>-20.4473</v>
       </c>
       <c r="R14" t="n">
-        <v>12.0035</v>
+        <v>11.6841</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6117</v>
+        <v>3.1378</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7233999999999997</v>
+        <v>1.4812</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8882</v>
+        <v>1.6566</v>
       </c>
       <c r="V14" t="n">
-        <v>6.499499999999999</v>
+        <v>6.539499999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>12.437</v>
+        <v>12.7179</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.937500000000001</v>
+        <v>-6.1784</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7636</v>
+        <v>4.2295</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9185</v>
+        <v>3.2718</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8451</v>
+        <v>0.9577</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8463</v>
+        <v>2.885</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3509</v>
+        <v>1.3742</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4954</v>
+        <v>1.5108</v>
       </c>
       <c r="J15" t="n">
-        <v>4.161</v>
+        <v>4.2692</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2794</v>
+        <v>2.34</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8816</v>
+        <v>1.9292</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3147</v>
+        <v>-1.3842</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9285</v>
+        <v>-0.9658</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3862</v>
+        <v>-0.4184</v>
       </c>
       <c r="P15" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R15" t="n">
-        <v>2.8008</v>
+        <v>2.7263</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0836</v>
+        <v>-0.5766</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7023</v>
+        <v>-0.4716</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3813</v>
+        <v>-0.105</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6709</v>
+        <v>3.6674</v>
       </c>
       <c r="E16" t="n">
-        <v>4.5871</v>
+        <v>2.2615</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9162</v>
+        <v>1.4059</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4354</v>
+        <v>-1.2067</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8236</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3881</v>
+        <v>-1.1246</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6008</v>
+        <v>0.5931</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4808</v>
+        <v>1.8244</v>
       </c>
       <c r="L16" t="n">
-        <v>0.12</v>
+        <v>-1.2312</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1654</v>
+        <v>-1.7998</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6573</v>
+        <v>-1.9065</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5081</v>
+        <v>0.1067</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0003</v>
+        <v>1.7526</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.2003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2006</v>
+        <v>2.7263</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9748</v>
+        <v>0.1204</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0671</v>
+        <v>-0.359</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9076</v>
+        <v>0.4794</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.7396</v>
+        <v>3.0011</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1195</v>
+        <v>3.0011</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.8591</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CASCALES FERNANDEZ</t>
+          <t>G. ALBA ASTOLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5966</v>
+        <v>2.9718</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1968</v>
+        <v>0.5665</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3998</v>
+        <v>2.4052</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0782</v>
+        <v>1.8561</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8736</v>
+        <v>1.3019</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2046</v>
+        <v>0.5542</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9794</v>
+        <v>2.1836</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0597</v>
+        <v>1.4702</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9197</v>
+        <v>0.7134</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0988</v>
+        <v>-0.3275</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1861</v>
+        <v>-0.1684</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2849</v>
+        <v>-0.1591</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6002</v>
+        <v>1.5579</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8005</v>
+        <v>2.7263</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1418</v>
+        <v>-0.7217</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0979</v>
+        <v>-0.7282</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2397</v>
+        <v>0.0064</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.2795</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6802</v>
+        <v>0.2795</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. ALBA ASTOLA</t>
+          <t>J. CASCALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5263</v>
+        <v>2.6308</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1758</v>
+        <v>1.211</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3505</v>
+        <v>1.4198</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8602</v>
+        <v>3.0569</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2865</v>
+        <v>0.859</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5736</v>
+        <v>2.1979</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0832</v>
+        <v>3.0332</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4014</v>
+        <v>1.0879</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6818</v>
+        <v>1.9453</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.223</v>
+        <v>0.0238</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1149</v>
+        <v>-0.2289</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1082</v>
+        <v>0.2527</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6005</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R18" t="n">
-        <v>2.8008</v>
+        <v>1.7526</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1941</v>
+        <v>-0.0688</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9669</v>
+        <v>0.0083</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2273</v>
+        <v>-0.0771</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2598</v>
+        <v>-0.9416</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2598</v>
+        <v>-0.6621</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.157</v>
+        <v>1.2158</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0441</v>
+        <v>1.2158</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1129</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2653</v>
+        <v>1.2158</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1854</v>
+        <v>1.2158</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3366</v>
+        <v>1.2158</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6849</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3484</v>
+        <v>1.2158</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6019</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7649</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.163</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8005</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8008</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2973</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2113</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.08599999999999999</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>2.9191</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.9191</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1998</v>
+        <v>1.0877</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1998</v>
+        <v>3.7969</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-2.7092</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1998</v>
+        <v>2.4622</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2.905</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1998</v>
+        <v>-0.4428</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1998</v>
+        <v>3.7266</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>3.605</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1998</v>
+        <v>0.1216</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-1.2644</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.5644</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1684</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.1421</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.425</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.0692</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.3558</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.7732</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1695</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-3.9426</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.096</v>
+        <v>0.9838</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5844</v>
+        <v>1.1845</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4884</v>
+        <v>-0.2007</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2041</v>
+        <v>1.2392</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0997</v>
+        <v>1.129</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1044</v>
+        <v>0.1103</v>
       </c>
       <c r="J21" t="n">
-        <v>1.705</v>
+        <v>1.8418</v>
       </c>
       <c r="K21" t="n">
-        <v>2.143</v>
+        <v>2.2631</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.438</v>
+        <v>-0.4213</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5009</v>
+        <v>-0.6025</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0433</v>
+        <v>-1.1342</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5424</v>
+        <v>0.5316</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5682</v>
+        <v>0.2967</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3801</v>
+        <v>0.0369</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1881</v>
+        <v>0.2598</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.9416</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0147</v>
+        <v>0.2722</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3642</v>
+        <v>0.4971</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3495</v>
+        <v>-0.2249</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2224</v>
+        <v>0.2079</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4468</v>
+        <v>0.4398</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2243</v>
+        <v>-0.2318</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6798</v>
+        <v>0.6974</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6398</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4574</v>
+        <v>-0.4895</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.193</v>
+        <v>-0.2171</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2643</v>
+        <v>-0.2724</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5481</v>
+        <v>-0.2404</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3156</v>
+        <v>-0.2003</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2325</v>
+        <v>-0.0401</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4958</v>
+        <v>-0.6435</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8006</v>
+        <v>-1.953</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3048</v>
+        <v>1.3095</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3411</v>
+        <v>-1.2649</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1899</v>
+        <v>-1.1206</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1512</v>
+        <v>-0.1442</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7688</v>
+        <v>-0.6176</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7326</v>
+        <v>-0.6259</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0362</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5723</v>
+        <v>-0.6473</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4573</v>
+        <v>-0.4947</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.115</v>
+        <v>-0.1526</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1545</v>
+        <v>-0.4049</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.031</v>
+        <v>-0.4144</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1234</v>
+        <v>0.0095</v>
       </c>
       <c r="V23" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.1346</v>
+        <v>-0.8207</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7433</v>
+        <v>2.0424</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3913</v>
+        <v>-2.8632</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8258</v>
+        <v>2.5434</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.9907</v>
+        <v>0.7435</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1649</v>
+        <v>1.7999</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2745</v>
+        <v>4.0959</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5544</v>
+        <v>1.7447</v>
       </c>
       <c r="L24" t="n">
-        <v>0.28</v>
+        <v>2.3512</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5513</v>
+        <v>-1.5525</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4363</v>
+        <v>-1.0013</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.115</v>
+        <v>-0.5513</v>
       </c>
       <c r="P24" t="n">
-        <v>1.2003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0003</v>
+        <v>-1.9474</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2006</v>
+        <v>0.9737</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6907</v>
+        <v>0.0517</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5314</v>
+        <v>-0.1061</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1592</v>
+        <v>0.1578</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.1998</v>
+        <v>-2.4421</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.1998</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.2945</v>
+        <v>-1.2966</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8838</v>
+        <v>-0.92</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.1783</v>
+        <v>-0.3767</v>
       </c>
       <c r="G25" t="n">
-        <v>2.4792</v>
+        <v>-1.9</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7917999999999999</v>
+        <v>-2.0311</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6874</v>
+        <v>0.1311</v>
       </c>
       <c r="J25" t="n">
-        <v>3.9087</v>
+        <v>-0.1909</v>
       </c>
       <c r="K25" t="n">
-        <v>1.6995</v>
+        <v>-0.4746</v>
       </c>
       <c r="L25" t="n">
-        <v>2.2092</v>
+        <v>0.2837</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.4295</v>
+        <v>-1.7091</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9077</v>
+        <v>-1.5565</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5218</v>
+        <v>-0.1526</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.0003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.0006</v>
+        <v>-0.9737</v>
       </c>
       <c r="R25" t="n">
-        <v>1.0003</v>
+        <v>2.1421</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3738</v>
+        <v>0.656</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0243</v>
+        <v>0.2446</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3495</v>
+        <v>0.4114</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.3995</v>
+        <v>-1.2211</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.3995</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.9227</v>
+        <v>-3.4099</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.6603</v>
+        <v>-1.2497</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.2624</v>
+        <v>-2.1602</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.6074</v>
+        <v>-2.5688</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.4131</v>
+        <v>-2.4395</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1943</v>
+        <v>-0.1293</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7068</v>
+        <v>-0.54</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.6344</v>
+        <v>-0.5567</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.07240000000000001</v>
+        <v>0.0167</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.9006</v>
+        <v>-2.0289</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.7787</v>
+        <v>-1.8828</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.1219</v>
+        <v>-0.146</v>
       </c>
       <c r="P26" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0843</v>
+        <v>0.6011</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0468</v>
+        <v>0.264</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0375</v>
+        <v>0.3371</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>8.177299999999999</v>
+        <v>10.8883</v>
       </c>
       <c r="E27" t="n">
-        <v>9.750299999999999</v>
+        <v>11.9248</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.573000000000001</v>
+        <v>-1.036800000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>8.285999999999998</v>
+        <v>8.5261</v>
       </c>
       <c r="H27" t="n">
-        <v>2.9992</v>
+        <v>3.079100000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>5.286799999999999</v>
+        <v>5.4473</v>
       </c>
       <c r="J27" t="n">
-        <v>18.9042</v>
+        <v>20.3081</v>
       </c>
       <c r="K27" t="n">
-        <v>12.4671</v>
+        <v>13.3349</v>
       </c>
       <c r="L27" t="n">
-        <v>6.4371</v>
+        <v>6.9733</v>
       </c>
       <c r="M27" t="n">
-        <v>-10.6182</v>
+        <v>-11.7819</v>
       </c>
       <c r="N27" t="n">
-        <v>-9.468</v>
+        <v>-10.2562</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.1502</v>
+        <v>-1.5258</v>
       </c>
       <c r="P27" t="n">
-        <v>9.0025</v>
+        <v>8.763199999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>-12.0034</v>
+        <v>-11.6842</v>
       </c>
       <c r="R27" t="n">
-        <v>21.006</v>
+        <v>20.4474</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.6116</v>
+        <v>0.1385000000000002</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.8883</v>
+        <v>-1.6566</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.7234999999999999</v>
+        <v>1.795</v>
       </c>
       <c r="V27" t="n">
-        <v>-6.499599999999999</v>
+        <v>-6.539499999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>4.737699999999999</v>
+        <v>4.9575</v>
       </c>
       <c r="X27" t="n">
-        <v>-11.2373</v>
+        <v>-11.497</v>
       </c>
     </row>
   </sheetData>
